--- a/www/download/IND.labour_force_value.s.mv.WIOD13.xlsx
+++ b/www/download/IND.labour_force_value.s.mv.WIOD13.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>7706.776</t>
+          <t>7705638591.72596</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8026.122</t>
+          <t>8025299577.8601</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>7822.12</t>
+          <t>7821327087.97977</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>8090.626</t>
+          <t>8090652430.08962</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8722.09</t>
+          <t>8874206533.63074</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8520.243</t>
+          <t>8519571354.02563</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8294.26</t>
+          <t>8292673556.00634</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8866.513</t>
+          <t>8864783710.90517</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>9634.378</t>
+          <t>9633480117.136</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>11420.688</t>
+          <t>11420464552.0776</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>12355.825</t>
+          <t>12355070947.2225</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>12302.128</t>
+          <t>12301519323.6663</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>12841.513</t>
+          <t>12839899739.9549</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>12577.568</t>
+          <t>12577473515.6806</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>12692.99</t>
+          <t>12692617887.0412</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4672.373</t>
+          <t>4671997960.05508</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4508.849</t>
+          <t>4509000928.97057</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3890.283</t>
+          <t>3890272592.23915</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4006.234</t>
+          <t>4006679804.8301</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4102.715</t>
+          <t>4154686202.73968</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3960.6</t>
+          <t>3960407923.74285</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4038.075</t>
+          <t>4038222056.20934</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4042.248</t>
+          <t>4041676557.09405</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>4416.84</t>
+          <t>4416213756.04254</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>4628.32</t>
+          <t>4628200675.86006</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>4702.023</t>
+          <t>4702135967.26963</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>4818.522</t>
+          <t>4818411710.20289</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>4872.564</t>
+          <t>4871510841.31536</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>4775.814</t>
+          <t>4775598715.59118</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>4334.862</t>
+          <t>4334722559.95287</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5790.402</t>
+          <t>5789924273.96474</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5902.218</t>
+          <t>5901733982.96789</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>5705.56</t>
+          <t>5705353345.29825</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5775.108</t>
+          <t>5775247085.73027</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>6436.424</t>
+          <t>6542399481.87736</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6791.497</t>
+          <t>6790449694.63374</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>7302.144</t>
+          <t>7301252824.01896</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>7876.621</t>
+          <t>7875261420.37654</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>9603.645</t>
+          <t>9602628260.51864</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>10185.642</t>
+          <t>10185704076.5201</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>10107.921</t>
+          <t>10107711126.3251</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>10087.969</t>
+          <t>10087817940.911</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>9732.892</t>
+          <t>9731546054.23637</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>8881.205</t>
+          <t>8880990299.43425</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>9184.12</t>
+          <t>9183682932.88638</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1317.181</t>
+          <t>1317099867.91282</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1184.698</t>
+          <t>1184652487.2136</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>996.602</t>
+          <t>996573885.625832</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1172.587</t>
+          <t>1172596939.52579</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1015.843</t>
+          <t>1037272196.08051</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>928.713</t>
+          <t>928682963.211546</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>942.196</t>
+          <t>942145045.535341</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>903.175</t>
+          <t>903084560.159302</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>929.798</t>
+          <t>929753688.578168</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>937.329</t>
+          <t>937345590.988989</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>931.606</t>
+          <t>931582992.869411</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>932.796</t>
+          <t>932719354.210187</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>999.208</t>
+          <t>999132617.710908</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1091.138</t>
+          <t>1091211311.12478</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1174.138</t>
+          <t>1174111829.78463</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>41422.505</t>
+          <t>41418701264.179</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>40133.482</t>
+          <t>40130550929.3093</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>38569.118</t>
+          <t>38566936316.5194</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>38632.391</t>
+          <t>38632480264.3739</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>36269.792</t>
+          <t>37060721662.8019</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>36375.488</t>
+          <t>36373642170.5247</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>35202.348</t>
+          <t>35198819947.0763</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>35234.51</t>
+          <t>35230340091.1818</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>35068.35</t>
+          <t>35067390814.1512</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>37102.962</t>
+          <t>37103598126.7397</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>39639.099</t>
+          <t>39637760672.8788</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>40868.156</t>
+          <t>40865055319.4741</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>41695.254</t>
+          <t>41690458469.4342</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>43770.875</t>
+          <t>43769488963.5848</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>44096.863</t>
+          <t>44094806225.1159</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>11808.17</t>
+          <t>11805094857.9676</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11447.437</t>
+          <t>11445573758.9851</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>10901.57</t>
+          <t>10899911509.1417</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>11823.388</t>
+          <t>11823287240.2428</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>12734.26</t>
+          <t>12992980563.0797</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>14211.838</t>
+          <t>14210741440.9037</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>15253.532</t>
+          <t>15249008109.7396</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>15470.381</t>
+          <t>15466181876.0861</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>16742.965</t>
+          <t>16741138123.1676</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>17806.574</t>
+          <t>17806476905.8912</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>19352.261</t>
+          <t>19350671913.7608</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>20405.895</t>
+          <t>20404662358.8748</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>19866.892</t>
+          <t>19864102435.1751</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>19756.59</t>
+          <t>19755601883.8484</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>17583.35</t>
+          <t>17581771667.9515</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>596946.554</t>
+          <t>596935865098.496</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>589384.384</t>
+          <t>589373076932.361</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>588155.812</t>
+          <t>588142877959.792</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>573910.41</t>
+          <t>573913721572.996</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>554733.979</t>
+          <t>565905599900.213</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>538289.059</t>
+          <t>538280143971.146</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>534277.285</t>
+          <t>534254771738.9</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>534591.93</t>
+          <t>534569551906.061</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>524814.726</t>
+          <t>524807492602.16</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>517399.98</t>
+          <t>517399537564.88</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>502177.166</t>
+          <t>502172451635.601</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>490227.056</t>
+          <t>490216554738.093</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>457334.038</t>
+          <t>457318223940.727</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>473774.183</t>
+          <t>473782249119.289</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>473622.407</t>
+          <t>473619848234.327</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>205.528</t>
+          <t>205502165.442021</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>213.651</t>
+          <t>213630679.915114</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>186.961</t>
+          <t>186947225.143701</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>197.477</t>
+          <t>197479290.059014</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>220.902</t>
+          <t>224960211.180862</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>220.557</t>
+          <t>220536803.809869</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>247.081</t>
+          <t>247046723.383002</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>257.565</t>
+          <t>257524220.903282</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>298.665</t>
+          <t>298639466.166068</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>289.618</t>
+          <t>289621412.642241</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>291.56</t>
+          <t>291553210.598619</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>299.284</t>
+          <t>299270826.295426</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>281.671</t>
+          <t>281642240.262292</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>342.224</t>
+          <t>342221459.922936</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>279.728</t>
+          <t>279717315.800882</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1872.402</t>
+          <t>1871823172.07116</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2675.494</t>
+          <t>2675441645.77356</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2469.505</t>
+          <t>2469459701.27879</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2447.534</t>
+          <t>2447591717.25913</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2374.425</t>
+          <t>2398355986.40787</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2269.636</t>
+          <t>2269561953.76971</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2381.157</t>
+          <t>2381088825.99375</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2437.213</t>
+          <t>2436875816.46255</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2609.165</t>
+          <t>2608992076.88731</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2841.202</t>
+          <t>2841310328.47695</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>3015.943</t>
+          <t>3015906480.33118</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2958.965</t>
+          <t>2958885776.95596</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>3085.173</t>
+          <t>3084818541.81761</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>3065.701</t>
+          <t>3065587136.59095</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2626.62</t>
+          <t>2626578649.59065</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>54873.719</t>
+          <t>54867962111.7238</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>49037.764</t>
+          <t>49047598624.2105</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>42615.308</t>
+          <t>42620428127.0143</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>44273.557</t>
+          <t>44279346885.924</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>45732.076</t>
+          <t>46374587781.9979</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>48108.871</t>
+          <t>48095612897.7597</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>46763.805</t>
+          <t>46785023967.0903</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>46252.327</t>
+          <t>46229661550.1477</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>52318.951</t>
+          <t>52296093750.6703</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>53100.679</t>
+          <t>53122048371.5862</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>50342.553</t>
+          <t>50353774669.2182</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>50583.825</t>
+          <t>50580121238.9316</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>52303.01</t>
+          <t>52273891540.2955</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>49903.449</t>
+          <t>49901218168.7529</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>46643.595</t>
+          <t>46642357730.4471</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4160.407</t>
+          <t>4160073931.75761</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4081.915</t>
+          <t>4081528739.86127</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3213.837</t>
+          <t>3213291967.70831</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>3599.513</t>
+          <t>3599752033.3781</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>3695.606</t>
+          <t>3750617029.96831</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3559.517</t>
+          <t>3559304165.71013</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3764.406</t>
+          <t>3764316466.72799</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>3878.948</t>
+          <t>3878518119.12255</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>4407.181</t>
+          <t>4406906402.79272</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>4426.1</t>
+          <t>4426142633.02633</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>4475.854</t>
+          <t>4475971389.54086</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>4608.817</t>
+          <t>4608643621.25642</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>4670.344</t>
+          <t>4669699708.97944</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>4450.549</t>
+          <t>4450391826.49546</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>3841.368</t>
+          <t>3841262157.65359</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>11814.983</t>
+          <t>11812798796.4288</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>11542.638</t>
+          <t>11541123397.5768</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>10274.243</t>
+          <t>10273502545.154</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>11738.279</t>
+          <t>11738914369.3987</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>13090.306</t>
+          <t>13299617746.6379</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>13593.35</t>
+          <t>13591566244.3714</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>14861.48</t>
+          <t>14859948948.9983</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>15956.629</t>
+          <t>15955176396.7674</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>18081.25</t>
+          <t>18079981989.2436</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>19315.097</t>
+          <t>19314406486.2421</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>20213.817</t>
+          <t>20213110499.9336</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>21296.156</t>
+          <t>21295500328.5464</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>21567.845</t>
+          <t>21566903254.4595</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>21111.595</t>
+          <t>21111276318.8337</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>17830.989</t>
+          <t>17830486135.1744</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>274.853</t>
+          <t>274811149.068064</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>288.486</t>
+          <t>288442271.662237</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>297.446</t>
+          <t>297425235.964501</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>309.941</t>
+          <t>309931465.833519</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>289.357</t>
+          <t>293887935.379961</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>330.65</t>
+          <t>330596747.151728</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>341.704</t>
+          <t>341593574.251427</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>429.922</t>
+          <t>429854851.804465</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>510.098</t>
+          <t>509924272.743985</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>523.693</t>
+          <t>523459619.868147</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>507.615</t>
+          <t>507583789.578934</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>522.81</t>
+          <t>522701403.122937</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>542.877</t>
+          <t>542821711.213754</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>591.877</t>
+          <t>591833200.674104</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>478.176</t>
+          <t>478141919.206822</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2225.829</t>
+          <t>2223242253.75322</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2297.254</t>
+          <t>2294049335.66189</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1992.343</t>
+          <t>1991336516.336</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2173.669</t>
+          <t>2172438531.84855</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2240.832</t>
+          <t>2268212178.77257</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2065.374</t>
+          <t>2063284150.26529</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2156.952</t>
+          <t>2155294104.96046</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2205.324</t>
+          <t>2204234708.12395</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2460.168</t>
+          <t>2459803244.90885</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2592.97</t>
+          <t>2592890769.5023</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2676.937</t>
+          <t>2676824110.22774</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2810.379</t>
+          <t>2810836951.61308</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2860.781</t>
+          <t>2860204413.46629</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2833.959</t>
+          <t>2833808673.6377</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2540.982</t>
+          <t>2540907123.4165</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>25801.795</t>
+          <t>25799208917.145</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>25961.766</t>
+          <t>25960000293.7528</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>22469.124</t>
+          <t>22467877462.7152</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25209.081</t>
+          <t>25209379462.3536</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>27502.757</t>
+          <t>27945025056.6959</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>27772.74</t>
+          <t>27766811147.7821</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>29706.683</t>
+          <t>29701200498.5202</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>30680.421</t>
+          <t>30676290339.9445</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>33375.745</t>
+          <t>33373410599.086</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>34647.628</t>
+          <t>34647850243.9643</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>34970.008</t>
+          <t>34966944041.255</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>34125.151</t>
+          <t>34122188108.8395</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>34304.544</t>
+          <t>34299257679.2793</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>33340.038</t>
+          <t>33338595613.1869</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>30444.903</t>
+          <t>30443946807.4977</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>24844.822</t>
+          <t>24843568406.3242</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>25390.317</t>
+          <t>25388683825.6383</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>24168.938</t>
+          <t>24168487553.0262</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>26636.347</t>
+          <t>26637338164.5381</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>28499.62</t>
+          <t>28943881743.6636</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>30030.276</t>
+          <t>30025761182.7746</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>31838.308</t>
+          <t>31835186732.9993</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>32739.649</t>
+          <t>32734747774.8261</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>34767.348</t>
+          <t>34764406212.126</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>37058.359</t>
+          <t>37058272214.1654</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>37411.613</t>
+          <t>37410638676.1209</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>37742.011</t>
+          <t>37740729948.1165</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>36934.586</t>
+          <t>36931554570.4039</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>32580.085</t>
+          <t>32578600661.2488</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>29297.368</t>
+          <t>29296454926.255</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2070.434</t>
+          <t>2070394197.68611</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2141.661</t>
+          <t>2141615818.87599</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2041.25</t>
+          <t>2041243041.10068</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2105.44</t>
+          <t>2105459725.05539</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2282.289</t>
+          <t>2301561409.69842</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2426.24</t>
+          <t>2426180454.01788</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2354.776</t>
+          <t>2354536206.69365</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2780.939</t>
+          <t>2780509934.11146</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2877.402</t>
+          <t>2877183786.04079</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2964.81</t>
+          <t>2964609798.68449</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2906.432</t>
+          <t>2906812584.05655</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>3148.041</t>
+          <t>3147877752.93182</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>3356.986</t>
+          <t>3356667993.11647</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>3408.651</t>
+          <t>3408238979.45791</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>3294.976</t>
+          <t>3294730924.33554</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2546.031</t>
+          <t>2545539043.77769</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2399.088</t>
+          <t>2398751974.78559</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2269.038</t>
+          <t>2268780075.77993</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2289.597</t>
+          <t>2289617075.4597</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2423.322</t>
+          <t>2486025144.54185</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2415.081</t>
+          <t>2414783130.11042</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2360.389</t>
+          <t>2360002082.33702</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2568.312</t>
+          <t>2567672504.67133</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2761.227</t>
+          <t>2760841804.2028</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2377.565</t>
+          <t>2377691490.86938</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2366.248</t>
+          <t>2366061165.52135</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2265.145</t>
+          <t>2264844781.76924</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2348.058</t>
+          <t>2347634030.84994</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2146.273</t>
+          <t>2146145193.73534</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1918.427</t>
+          <t>1918375375.99126</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>25158.044</t>
+          <t>25157611384.0289</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>25499.06</t>
+          <t>25498675818.5522</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>22957.016</t>
+          <t>22956710466.2717</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>21833.5</t>
+          <t>21833525037.9708</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>24213.579</t>
+          <t>24342663859.2452</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>25959.248</t>
+          <t>25959097322.3074</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>27084.571</t>
+          <t>27084239404.1906</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>28483.407</t>
+          <t>28482880064.3255</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>30604.834</t>
+          <t>30604597989.7027</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>31255.713</t>
+          <t>31255739862.2941</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>29672.698</t>
+          <t>29672510657.7043</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>29671.827</t>
+          <t>29671537164.711</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>31689.842</t>
+          <t>31689289582.1787</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>31472.947</t>
+          <t>31473078123.9444</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>33742.451</t>
+          <t>33742110359.1757</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>290062.905</t>
+          <t>290057152894.741</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>272364.224</t>
+          <t>272359861296.22</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>288094.284</t>
+          <t>288089845933.904</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>285955.942</t>
+          <t>285956649283.872</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>279015.366</t>
+          <t>281404773216.484</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>281644.902</t>
+          <t>281638724625.021</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>290738.895</t>
+          <t>290726664104.82</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>277148.716</t>
+          <t>277138193974.188</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>299847.573</t>
+          <t>299843908163.794</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>314133.673</t>
+          <t>314134145916.316</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>326465.997</t>
+          <t>326464344701.039</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>330867.061</t>
+          <t>330858668621.859</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>312992.782</t>
+          <t>312985734545.041</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>305453.645</t>
+          <t>305461880460.554</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>321513.186</t>
+          <t>321512023369.064</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1235.452</t>
+          <t>1235060164.55085</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1321.241</t>
+          <t>1321019544.53951</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1205.704</t>
+          <t>1205556642.54143</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1243.342</t>
+          <t>1243310651.90305</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1312.784</t>
+          <t>1332243628.4394</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1390.447</t>
+          <t>1390219696.99494</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1591.902</t>
+          <t>1591651611.15825</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1710.152</t>
+          <t>1709894997.59156</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1569.116</t>
+          <t>1568941181.00444</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1530.49</t>
+          <t>1530477491.213</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1803.652</t>
+          <t>1803508630.20746</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>1866.26</t>
+          <t>1866186237.70102</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2070.34</t>
+          <t>2070004207.98799</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2096.342</t>
+          <t>2096221701.63602</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2076.953</t>
+          <t>2076878749.15174</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>17613.336</t>
+          <t>17608689718.658</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>17479.367</t>
+          <t>17472747607.6986</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>16093.183</t>
+          <t>16089458358.895</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>16390.316</t>
+          <t>16392442868.4492</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>16824.241</t>
+          <t>16986809022.0075</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>17058.989</t>
+          <t>17056516641.5532</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>18132.308</t>
+          <t>18132295715.958</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>18988.218</t>
+          <t>18982988488.9827</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>21156.202</t>
+          <t>21153133727.0089</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>22688.171</t>
+          <t>22688330566.0101</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>23029.478</t>
+          <t>23029458164.0615</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>23853.245</t>
+          <t>23851520552.9715</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>23054.047</t>
+          <t>23051433248.0521</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>21860.311</t>
+          <t>21859683676.1317</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>19207.654</t>
+          <t>19206827182.4652</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>82640.455</t>
+          <t>82597514690.6315</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>73505.152</t>
+          <t>73484441933.2932</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>65862.013</t>
+          <t>65844406003.3795</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>62507.183</t>
+          <t>62505859081.0421</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>65353.06</t>
+          <t>66083056234.906</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>69792.88</t>
+          <t>69797683295.2722</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>68456.94</t>
+          <t>68417373387.652</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>64425.702</t>
+          <t>64389403438.4576</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>66258.207</t>
+          <t>66230163044.2589</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>70223.893</t>
+          <t>70190658692.961</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>69857.034</t>
+          <t>69823269472.1311</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>67976.283</t>
+          <t>68008170858.0222</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>61742.964</t>
+          <t>61730661018.8571</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>58684.675</t>
+          <t>58677661016.6217</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>56380.388</t>
+          <t>56414187843.6038</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>19870.239</t>
+          <t>19867654482.6334</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>19356.813</t>
+          <t>19354607615.1318</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>17753.367</t>
+          <t>17751351782.5212</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>14788.414</t>
+          <t>14788621583.1125</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>15128.465</t>
+          <t>15408052573.9551</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>16359.771</t>
+          <t>16358004816.2097</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>16615.458</t>
+          <t>16610774947.207</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>17410.753</t>
+          <t>17405937348.9905</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>18876.923</t>
+          <t>18874667181.8763</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>20134.114</t>
+          <t>20133000533.9385</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>20262.716</t>
+          <t>20261057197.436</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>21239.473</t>
+          <t>21237881116.0136</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>20641.072</t>
+          <t>20637904071.2022</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>19013.475</t>
+          <t>19015599201.1569</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>17967.595</t>
+          <t>17967497457.859</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>616.521</t>
+          <t>616580783.465646</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>623.417</t>
+          <t>623469522.716759</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>617.506</t>
+          <t>617453605.738561</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>757.901</t>
+          <t>757868298.247496</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>774.543</t>
+          <t>782720380.586799</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>791.981</t>
+          <t>791985808.613802</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>751.989</t>
+          <t>751886605.65256</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>791.218</t>
+          <t>791121566.369054</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>888.081</t>
+          <t>888220930.986592</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>783.56</t>
+          <t>783600008.952876</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>857.928</t>
+          <t>857770259.591309</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>908.246</t>
+          <t>908071604.116458</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>919.675</t>
+          <t>919590933.723099</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>1005.508</t>
+          <t>1005507960.24553</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>885.023</t>
+          <t>885020479.869291</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>294.067</t>
+          <t>294037718.506836</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>260.606</t>
+          <t>260594703.353464</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>227.027</t>
+          <t>227018941.436308</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>233.731</t>
+          <t>233740844.176465</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>259.836</t>
+          <t>265485256.055827</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>280.332</t>
+          <t>280276272.867663</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>269.455</t>
+          <t>269450534.129408</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>296.582</t>
+          <t>296497598.973242</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>317.085</t>
+          <t>317011824.168345</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>338.352</t>
+          <t>338384271.960619</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>363.862</t>
+          <t>363859259.083543</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>364.779</t>
+          <t>364758296.06385</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>335.11</t>
+          <t>335007408.463278</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>393.805</t>
+          <t>393800105.703462</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>339.095</t>
+          <t>339079975.843886</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>362.956</t>
+          <t>362901623.183509</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>385.258</t>
+          <t>385217989.07204</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>371.46</t>
+          <t>371432934.136889</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>395.424</t>
+          <t>395421708.480583</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>397.292</t>
+          <t>401661917.019753</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>343.18</t>
+          <t>343142195.62016</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>331.99</t>
+          <t>331934381.498462</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>324.44</t>
+          <t>324398486.65673</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>348.842</t>
+          <t>348815893.88037</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>351.746</t>
+          <t>351743175.844331</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>383.662</t>
+          <t>383636799.134671</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>429.92</t>
+          <t>429857365.794392</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>514.589</t>
+          <t>514522146.312162</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>570.572</t>
+          <t>570644524.275713</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>424.257</t>
+          <t>424253225.595565</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>10884.173</t>
+          <t>10883463466.8764</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>10727.26</t>
+          <t>10726721964.9098</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>10576.79</t>
+          <t>10576143063.0118</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>11706.65</t>
+          <t>11706792845.5579</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>12816.891</t>
+          <t>13082847404.5304</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>13664.063</t>
+          <t>13663563872.4705</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>15420.096</t>
+          <t>15416951341.9321</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>15499.29</t>
+          <t>15495886557.4276</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>15705.562</t>
+          <t>15704515999.2756</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>15718.774</t>
+          <t>15718557669.1707</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>15607.599</t>
+          <t>15606793931.8182</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>15211.4</t>
+          <t>15210178394.0724</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>14886.815</t>
+          <t>14885091302.0006</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>15552.083</t>
+          <t>15552523607.0067</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>15251.545</t>
+          <t>15251178016.0497</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>99.104</t>
+          <t>99089723.0459217</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>106.148</t>
+          <t>106134848.895005</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>86.578</t>
+          <t>86570462.2458659</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>94.674</t>
+          <t>94677772.0587103</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>107.666</t>
+          <t>109637939.817902</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>115.059</t>
+          <t>115046272.944031</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>131.174</t>
+          <t>131160623.634574</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>140.079</t>
+          <t>140055541.082736</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>154.711</t>
+          <t>154697343.947979</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>121.111</t>
+          <t>121113851.622106</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>122.485</t>
+          <t>122482498.226379</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>119.834</t>
+          <t>119828933.713333</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>130.898</t>
+          <t>130880074.544293</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>146.007</t>
+          <t>146003708.150769</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>126.67</t>
+          <t>126666757.708984</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>11975.96</t>
+          <t>11975638300.6216</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>11606.789</t>
+          <t>11607150394.7498</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>8206.472</t>
+          <t>8205964824.41684</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>10224.91</t>
+          <t>10225203042.2481</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>11107.955</t>
+          <t>11268626536.246</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>10696.403</t>
+          <t>10696119570.969</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>12038.016</t>
+          <t>12037474594.8428</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>13431.588</t>
+          <t>13430492323.8696</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>13172.052</t>
+          <t>13171665205.3933</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>12833.442</t>
+          <t>12834168455.4736</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>12424.649</t>
+          <t>12424837401.0541</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>12635.416</t>
+          <t>12635137110.2124</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>12848.714</t>
+          <t>12847218189.5279</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>13558.943</t>
+          <t>13558744484.1056</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>12868.262</t>
+          <t>12867964972.6057</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>8302.471</t>
+          <t>8301896246.35584</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8756.19</t>
+          <t>8755768497.61343</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>8980.636</t>
+          <t>8980249880.78167</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>9322.448</t>
+          <t>9322532659.46263</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>8856.906</t>
+          <t>8930322372.33043</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>8619.64</t>
+          <t>8619225957.88915</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>7269.152</t>
+          <t>7268571557.41968</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>6772.718</t>
+          <t>6771951250.5466</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>6525.7</t>
+          <t>6525347883.08909</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>6291.131</t>
+          <t>6291207664.17717</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>6693.326</t>
+          <t>6693033204.31113</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>6818.15</t>
+          <t>6817455222.66778</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>7147.104</t>
+          <t>7146220200.48576</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>7739.008</t>
+          <t>7738815384.68595</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>6915.834</t>
+          <t>6915723117.89042</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>3446.449</t>
+          <t>3446204736.26788</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3501.074</t>
+          <t>3500874130.8758</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>3030.531</t>
+          <t>3030410233.01685</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>3381.477</t>
+          <t>3381534261.08586</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>3430.407</t>
+          <t>3479745652.68562</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3556.962</t>
+          <t>3556714273.53046</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3747.414</t>
+          <t>3747127904.5967</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>3748.434</t>
+          <t>3748030831.57336</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>3795.017</t>
+          <t>3794751319.631</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>3823.821</t>
+          <t>3823851030.49597</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>3781.319</t>
+          <t>3781241353.21305</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>3614.812</t>
+          <t>3614612636.9678</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>3621.003</t>
+          <t>3620715828.96472</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>3738.756</t>
+          <t>3738822510.89181</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>3117.643</t>
+          <t>3117563936.4603</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>4556.109</t>
+          <t>4555943491.0419</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>4544.977</t>
+          <t>4544852988.26497</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3742.185</t>
+          <t>3742081544.03276</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>4493.324</t>
+          <t>4493381146.06479</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>5216.98</t>
+          <t>5249201799.807</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6012.619</t>
+          <t>6012498855.33855</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>6343.908</t>
+          <t>6343714846.54533</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>5013.093</t>
+          <t>5012775393.58699</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>4986.8</t>
+          <t>4986649157.08499</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>4453.149</t>
+          <t>4453194634.70144</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>4901.182</t>
+          <t>4901011248.92804</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>4802.552</t>
+          <t>4801732239.74897</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>5100.749</t>
+          <t>5100182078.15977</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>5535.76</t>
+          <t>5536502720.07461</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>5000.694</t>
+          <t>5000625464.22793</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>56931.836</t>
+          <t>56928659815.6748</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>59226.26</t>
+          <t>59223704477.0546</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>53649.128</t>
+          <t>53647794248.7393</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>48547.707</t>
+          <t>48548425216.4321</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>45287.527</t>
+          <t>45575564034.4157</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>50888.842</t>
+          <t>50887819684.7672</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>49817.636</t>
+          <t>49814420329.5061</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>51411.157</t>
+          <t>51407940678.5592</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>55835.887</t>
+          <t>55834495648.2248</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>58723.866</t>
+          <t>58724323770.0509</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>61724.372</t>
+          <t>61722960444.6255</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>61727.963</t>
+          <t>61723417758.2888</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>68904.51</t>
+          <t>68899969480.2054</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>73795.621</t>
+          <t>73801722942.5701</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>72594.946</t>
+          <t>72594580411.1789</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>689.46</t>
+          <t>689371171.856937</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>741.415</t>
+          <t>741363294.319116</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>707.335</t>
+          <t>707273580.336595</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>701.189</t>
+          <t>701191821.244031</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>636.36</t>
+          <t>646362120.784476</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>638.991</t>
+          <t>638962884.190443</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>650.585</t>
+          <t>650477510.310293</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>644.289</t>
+          <t>644187223.972571</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>724.855</t>
+          <t>724861538.85442</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>878.729</t>
+          <t>878758843.235585</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>896.437</t>
+          <t>896348131.582911</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>963.457</t>
+          <t>963429449.245739</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>1169.084</t>
+          <t>1169345981.97149</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>1146.199</t>
+          <t>1146284495.46643</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>1305.383</t>
+          <t>1305388336.70176</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>875.253</t>
+          <t>875017249.501707</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>836.314</t>
+          <t>836193860.043109</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>725.046</t>
+          <t>724965388.143781</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>764.913</t>
+          <t>764902189.198663</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>776.477</t>
+          <t>789301634.56469</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>783.674</t>
+          <t>783626325.732608</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>816.132</t>
+          <t>816191754.479968</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>832.315</t>
+          <t>832267124.338991</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>928.574</t>
+          <t>928552104.112743</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>883.883</t>
+          <t>884025817.519957</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>853.106</t>
+          <t>853200350.402396</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>858.451</t>
+          <t>858453733.508722</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>862.77</t>
+          <t>862604228.787207</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>1199.451</t>
+          <t>1199318907.2303</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>1148.724</t>
+          <t>1148590044.8546</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>4836.145</t>
+          <t>4834708205.44326</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4955.592</t>
+          <t>4954618997.28642</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>4248.214</t>
+          <t>4247502193.57569</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>4634.039</t>
+          <t>4633892920.44269</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>4766.689</t>
+          <t>4855889940.48511</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>5239.529</t>
+          <t>5238558044.09226</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5334.795</t>
+          <t>5333662269.94917</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>5490.902</t>
+          <t>5489879457.69971</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>5875.842</t>
+          <t>5875036803.17672</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>6080.401</t>
+          <t>6080491613.86417</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>6258.896</t>
+          <t>6258366816.83808</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>6307.547</t>
+          <t>6307162020.79335</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>6691.737</t>
+          <t>6690757109.13023</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>6035.202</t>
+          <t>6034975032.64706</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>5130.118</t>
+          <t>5130000063.20627</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>7558.891</t>
+          <t>7558499221.98414</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8667.815</t>
+          <t>8667492723.52426</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>9079.881</t>
+          <t>9079399159.75798</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>8923.76</t>
+          <t>8923882730.78617</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>9530.251</t>
+          <t>9685677906.9974</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>8569.109</t>
+          <t>8568644384.59602</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>7760.494</t>
+          <t>7759682546.83582</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>7029.191</t>
+          <t>7028230603.35858</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>7329.968</t>
+          <t>7329565553.38878</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>7869.734</t>
+          <t>7869647544.68591</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>7829.612</t>
+          <t>7829423115.16001</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>7508.452</t>
+          <t>7507769902.84978</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>7519.044</t>
+          <t>7518205478.5912</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>13076.689</t>
+          <t>13077081338.7786</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>11502.362</t>
+          <t>11501997293.0901</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>9113.996</t>
+          <t>9112434490.78151</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>9657.874</t>
+          <t>9656808740.5278</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>8775.3</t>
+          <t>8774272368.44252</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>8397.601</t>
+          <t>8397593245.82903</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>8296.314</t>
+          <t>8444403301.08271</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>8910.149</t>
+          <t>8909375762.16233</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>8659.551</t>
+          <t>8656943285.31329</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>8541.101</t>
+          <t>8538462373.67667</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>8711.03</t>
+          <t>8710117288.81314</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>8912.351</t>
+          <t>8911883358.45238</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>8985.529</t>
+          <t>8984695168.24755</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>8845.457</t>
+          <t>8845528057.48495</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>8100.793</t>
+          <t>8099756709.52454</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>8202.819</t>
+          <t>8202454914.50187</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>7193.987</t>
+          <t>7194040692.8739</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>127117.342</t>
+          <t>127070069485.76</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>126819.462</t>
+          <t>126787804534.312</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>130495.878</t>
+          <t>130460113971.652</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>140827.921</t>
+          <t>140824741627.38</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>148007.369</t>
+          <t>149562599862.172</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>166667.124</t>
+          <t>166643368346.981</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>171727.13</t>
+          <t>171677291074.399</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>174676.567</t>
+          <t>174623988393.665</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>179798.995</t>
+          <t>179781635268.629</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>185318.581</t>
+          <t>185306093472.436</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>189054.025</t>
+          <t>189070053164.507</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>187923.467</t>
+          <t>187925416849.469</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>176109.673</t>
+          <t>176073754221.994</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>164200.05</t>
+          <t>164218422192.036</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>153642.359</t>
+          <t>153641084521.774</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>742448.71</t>
+          <t>742433811909.135</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>740936.338</t>
+          <t>740926016608.316</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>767960.538</t>
+          <t>767946706372.796</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>775860.238</t>
+          <t>775863927108.53</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>801483.282</t>
+          <t>816558364484.71</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>851036.789</t>
+          <t>851033003432.735</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>874236.658</t>
+          <t>874219900187.244</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>883623.229</t>
+          <t>883599151577.978</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>895601.324</t>
+          <t>895590055184.604</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>890900.963</t>
+          <t>890899931914.113</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>924148.135</t>
+          <t>924141739499.986</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>955103.176</t>
+          <t>955080878904.449</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>923173.991</t>
+          <t>923147726077.342</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>943236.368</t>
+          <t>943262292215.854</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>940203.039</t>
+          <t>940200668438.331</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2227044.637</t>
+          <t>2226881257034.23</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2188495.868</t>
+          <t>2188396897296.65</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2191485.132</t>
+          <t>2191384714107.59</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2196377.781</t>
+          <t>2196392032002.47</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2215966.832</t>
+          <t>2252100609844.7</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2290890.413</t>
+          <t>2290809816738.57</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2330012.83</t>
+          <t>2329851971928.72</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2333605.768</t>
+          <t>2333386561634.62</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2394691.084</t>
+          <t>2394575687201.53</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2423868.866</t>
+          <t>2423842961021.48</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2464422.182</t>
+          <t>2464388167341.6</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2489620.335</t>
+          <t>2489585994514.54</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2399825.543</t>
+          <t>2399656543905.74</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2416116.012</t>
+          <t>2416168572265.36</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2390424.026</t>
+          <t>2390438471112.01</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>labour_force_value.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD13</t>
